--- a/artfynd/A 39598-2026 artfynd.xlsx
+++ b/artfynd/A 39598-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136583149</v>
       </c>
       <c r="B3" t="n">
-        <v>92541</v>
+        <v>92543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>136583148</v>
       </c>
       <c r="B5" t="n">
-        <v>104874</v>
+        <v>104876</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39598-2026 artfynd.xlsx
+++ b/artfynd/A 39598-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>88627120</v>
+        <v>136940447</v>
       </c>
       <c r="B6" t="n">
-        <v>80392</v>
+        <v>104876</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,21 +1130,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>222412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1154,19 +1154,19 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kloten, Dlr</t>
+          <t>Kloten - Gruvens, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518344</v>
+        <v>518375</v>
       </c>
       <c r="R6" t="n">
-        <v>6639742</v>
+        <v>6639808</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-10-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-10-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,6 +1209,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1223,6 +1228,117 @@
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136940447</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>88627120</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kloten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>518344</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6639742</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-10-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-10-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/88627120</t>
         </is>
@@ -1235,6 +1351,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39598-2026 artfynd.xlsx
+++ b/artfynd/A 39598-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136583149</v>
       </c>
       <c r="B3" t="n">
-        <v>92543</v>
+        <v>92545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>136583148</v>
       </c>
       <c r="B5" t="n">
-        <v>104876</v>
+        <v>104882</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>136940447</v>
       </c>
       <c r="B6" t="n">
-        <v>104876</v>
+        <v>104882</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39598-2026 artfynd.xlsx
+++ b/artfynd/A 39598-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136583149</v>
       </c>
       <c r="B3" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>136583148</v>
       </c>
       <c r="B5" t="n">
-        <v>104882</v>
+        <v>104884</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>136940447</v>
       </c>
       <c r="B6" t="n">
-        <v>104882</v>
+        <v>104884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39598-2026 artfynd.xlsx
+++ b/artfynd/A 39598-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136583149</v>
       </c>
       <c r="B3" t="n">
-        <v>92547</v>
+        <v>92548</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>136583148</v>
       </c>
       <c r="B5" t="n">
-        <v>104884</v>
+        <v>104885</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>136940447</v>
       </c>
       <c r="B6" t="n">
-        <v>104884</v>
+        <v>104885</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39598-2026 artfynd.xlsx
+++ b/artfynd/A 39598-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136583149</v>
       </c>
       <c r="B3" t="n">
-        <v>92548</v>
+        <v>92554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>136583148</v>
       </c>
       <c r="B5" t="n">
-        <v>104885</v>
+        <v>104891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>136940447</v>
       </c>
       <c r="B6" t="n">
-        <v>104885</v>
+        <v>104891</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39598-2026 artfynd.xlsx
+++ b/artfynd/A 39598-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136583149</v>
       </c>
       <c r="B3" t="n">
-        <v>92554</v>
+        <v>92558</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>136583148</v>
       </c>
       <c r="B5" t="n">
-        <v>104891</v>
+        <v>104895</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>136940447</v>
       </c>
       <c r="B6" t="n">
-        <v>104891</v>
+        <v>104895</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39598-2026 artfynd.xlsx
+++ b/artfynd/A 39598-2026 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>136583148</v>
       </c>
       <c r="B5" t="n">
-        <v>104895</v>
+        <v>104897</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>136940447</v>
       </c>
       <c r="B6" t="n">
-        <v>104895</v>
+        <v>104897</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39598-2026 artfynd.xlsx
+++ b/artfynd/A 39598-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136583149</v>
       </c>
       <c r="B3" t="n">
-        <v>92558</v>
+        <v>92560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>136583148</v>
       </c>
       <c r="B5" t="n">
-        <v>104897</v>
+        <v>104899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>136940447</v>
       </c>
       <c r="B6" t="n">
-        <v>104897</v>
+        <v>104899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39598-2026 artfynd.xlsx
+++ b/artfynd/A 39598-2026 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>136940447</v>
       </c>
       <c r="B6" t="n">
-        <v>104899</v>
+        <v>104912</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39598-2026 artfynd.xlsx
+++ b/artfynd/A 39598-2026 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>136940447</v>
       </c>
       <c r="B6" t="n">
-        <v>104912</v>
+        <v>104914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39598-2026 artfynd.xlsx
+++ b/artfynd/A 39598-2026 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>136940447</v>
       </c>
       <c r="B6" t="n">
-        <v>104914</v>
+        <v>104917</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39598-2026 artfynd.xlsx
+++ b/artfynd/A 39598-2026 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>136940447</v>
       </c>
       <c r="B6" t="n">
-        <v>104917</v>
+        <v>104936</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39598-2026 artfynd.xlsx
+++ b/artfynd/A 39598-2026 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>136940447</v>
       </c>
       <c r="B6" t="n">
-        <v>104936</v>
+        <v>104937</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39598-2026 artfynd.xlsx
+++ b/artfynd/A 39598-2026 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>136940447</v>
       </c>
       <c r="B6" t="n">
-        <v>104937</v>
+        <v>104942</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39598-2026 artfynd.xlsx
+++ b/artfynd/A 39598-2026 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>136940447</v>
       </c>
       <c r="B6" t="n">
-        <v>104942</v>
+        <v>104945</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39598-2026 artfynd.xlsx
+++ b/artfynd/A 39598-2026 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>136940447</v>
       </c>
       <c r="B6" t="n">
-        <v>104945</v>
+        <v>104951</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39598-2026 artfynd.xlsx
+++ b/artfynd/A 39598-2026 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>136940447</v>
       </c>
       <c r="B6" t="n">
-        <v>104951</v>
+        <v>104952</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39598-2026 artfynd.xlsx
+++ b/artfynd/A 39598-2026 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>136940447</v>
       </c>
       <c r="B6" t="n">
-        <v>104952</v>
+        <v>104964</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39598-2026 artfynd.xlsx
+++ b/artfynd/A 39598-2026 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>136940447</v>
       </c>
       <c r="B6" t="n">
-        <v>104964</v>
+        <v>104965</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39598-2026 artfynd.xlsx
+++ b/artfynd/A 39598-2026 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>136940447</v>
       </c>
       <c r="B6" t="n">
-        <v>104965</v>
+        <v>104968</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39598-2026 artfynd.xlsx
+++ b/artfynd/A 39598-2026 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>136940447</v>
       </c>
       <c r="B6" t="n">
-        <v>104968</v>
+        <v>104970</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39598-2026 artfynd.xlsx
+++ b/artfynd/A 39598-2026 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>136940447</v>
       </c>
       <c r="B6" t="n">
-        <v>104970</v>
+        <v>104974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
